--- a/grupos/1AM - Estadisticos 20221.xlsx
+++ b/grupos/1AM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="151">
   <si>
     <t>Materia</t>
   </si>
@@ -224,229 +224,229 @@
     <t>CRUZ</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>JERONIMO</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>GILES</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>EDER</t>
+  </si>
+  <si>
+    <t>NORBERTO DAMIAN</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>ANGELO</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>DIEGO JESUS</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>DIERICK YAEL</t>
+  </si>
+  <si>
+    <t>SHERLIN</t>
+  </si>
+  <si>
+    <t>SAUL AZAEL</t>
+  </si>
+  <si>
+    <t>EIDAN JOSEPH</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>ARGUELLES</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>MEJIA</t>
   </si>
   <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>JERONIMO</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>GILES</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>EDER</t>
-  </si>
-  <si>
-    <t>NORBERTO DAMIAN</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ANGELO</t>
+    <t>MERINO</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
+  </si>
+  <si>
+    <t>ROCETE</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>GALVAN</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>RUBEN DE JESUS</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>CHRISTOPHER</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>LUIS FERNANDO</t>
   </si>
   <si>
     <t>ANA KAREN</t>
   </si>
   <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>DIEGO JESUS</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>DIERICK YAEL</t>
+    <t>ISABEL</t>
+  </si>
+  <si>
+    <t>JESUS YAEL</t>
+  </si>
+  <si>
+    <t>GABAEL</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
   </si>
   <si>
     <t>JOSE FRANCISCO</t>
-  </si>
-  <si>
-    <t>SHERLIN</t>
-  </si>
-  <si>
-    <t>SAUL AZAEL</t>
-  </si>
-  <si>
-    <t>EIDAN JOSEPH</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>ARGUELLES</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MERINO</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
-    <t>ROCETE</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>GALVAN</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>RUBEN DE JESUS</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>CHRISTOPHER</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>LUIS FERNANDO</t>
-  </si>
-  <si>
-    <t>ISABEL</t>
-  </si>
-  <si>
-    <t>JESUS YAEL</t>
-  </si>
-  <si>
-    <t>GABAEL</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
   </si>
   <si>
     <t>CESAR</t>
@@ -974,10 +974,10 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
         <v>-1</v>
@@ -986,7 +986,7 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -1010,7 +1010,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U4">
         <v>10</v>
@@ -1051,10 +1051,10 @@
         <v>7</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
         <v>-1</v>
@@ -1063,7 +1063,7 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1090,7 +1090,7 @@
         <v>7</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -1128,10 +1128,10 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>-1</v>
@@ -1140,7 +1140,7 @@
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1167,7 +1167,7 @@
         <v>7</v>
       </c>
       <c r="U6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>5</v>
@@ -1205,10 +1205,10 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
         <v>-1</v>
@@ -1217,7 +1217,7 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1241,7 +1241,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>10</v>
@@ -1253,7 +1253,7 @@
         <v>9</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -1282,10 +1282,10 @@
         <v>6</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>-1</v>
@@ -1294,7 +1294,7 @@
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1318,7 +1318,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>10</v>
@@ -1330,7 +1330,7 @@
         <v>9</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>6</v>
@@ -1359,7 +1359,7 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1371,7 +1371,7 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1395,7 +1395,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>-1</v>
@@ -1430,16 +1430,16 @@
         <v>6</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G10">
         <v>5</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>-1</v>
@@ -1448,7 +1448,7 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1484,7 +1484,7 @@
         <v>6</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y10">
         <v>5</v>
@@ -1507,13 +1507,13 @@
         <v>5</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G11">
         <v>5</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1525,7 +1525,7 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1561,7 +1561,7 @@
         <v>5</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -1590,10 +1590,10 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
         <v>-1</v>
@@ -1602,7 +1602,7 @@
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1626,7 +1626,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U12">
         <v>6</v>
@@ -1661,13 +1661,13 @@
         <v>7</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1703,7 +1703,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>-1</v>
@@ -1715,7 +1715,7 @@
         <v>7</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1744,7 +1744,7 @@
         <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1756,7 +1756,7 @@
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1792,7 +1792,7 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>6</v>
@@ -1821,10 +1821,10 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J15">
         <v>-1</v>
@@ -1833,7 +1833,7 @@
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1857,7 +1857,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>10</v>
@@ -1869,7 +1869,7 @@
         <v>8</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -1898,7 +1898,7 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -1910,7 +1910,7 @@
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -1975,10 +1975,10 @@
         <v>7</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
         <v>-1</v>
@@ -1987,7 +1987,7 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -2014,7 +2014,7 @@
         <v>9</v>
       </c>
       <c r="U17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -2023,7 +2023,7 @@
         <v>9</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>7</v>
@@ -2046,13 +2046,13 @@
         <v>5</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G18">
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2064,7 +2064,7 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2100,7 +2100,7 @@
         <v>5</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -2129,10 +2129,10 @@
         <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>-1</v>
@@ -2141,7 +2141,7 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2165,7 +2165,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U19">
         <v>10</v>
@@ -2177,7 +2177,7 @@
         <v>9</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2206,10 +2206,10 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
         <v>-1</v>
@@ -2283,7 +2283,7 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2295,7 +2295,7 @@
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2360,10 +2360,10 @@
         <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J22">
         <v>-1</v>
@@ -2437,10 +2437,10 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
         <v>-1</v>
@@ -2449,7 +2449,7 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2476,7 +2476,7 @@
         <v>7</v>
       </c>
       <c r="U23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>5</v>
@@ -2508,13 +2508,13 @@
         <v>5</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G24">
         <v>6</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -2526,7 +2526,7 @@
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2562,7 +2562,7 @@
         <v>5</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y24">
         <v>6</v>
@@ -2591,10 +2591,10 @@
         <v>7</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
         <v>-1</v>
@@ -2603,7 +2603,7 @@
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2627,7 +2627,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>10</v>
@@ -2662,16 +2662,16 @@
         <v>8</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G26">
         <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
         <v>-1</v>
@@ -2680,7 +2680,7 @@
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2716,7 +2716,7 @@
         <v>8</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y26">
         <v>6</v>
@@ -2745,10 +2745,10 @@
         <v>6</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
         <v>-1</v>
@@ -2757,7 +2757,7 @@
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2781,10 +2781,10 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>9</v>
@@ -2816,13 +2816,13 @@
         <v>5</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G28">
         <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -2834,7 +2834,7 @@
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2870,7 +2870,7 @@
         <v>5</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y28">
         <v>5</v>
@@ -2899,10 +2899,10 @@
         <v>9</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J29">
         <v>-1</v>
@@ -2911,7 +2911,7 @@
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -2935,10 +2935,10 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -2976,10 +2976,10 @@
         <v>7</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
         <v>-1</v>
@@ -2988,7 +2988,7 @@
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -3012,7 +3012,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U30">
         <v>10</v>
@@ -3053,10 +3053,10 @@
         <v>8</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
         <v>-1</v>
@@ -3065,7 +3065,7 @@
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3089,7 +3089,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>10</v>
@@ -3130,10 +3130,10 @@
         <v>9</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
         <v>-1</v>
@@ -3142,7 +3142,7 @@
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3166,10 +3166,10 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V32">
         <v>9</v>
@@ -3178,7 +3178,7 @@
         <v>8</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y32">
         <v>9</v>
@@ -3207,7 +3207,7 @@
         <v>6</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -3219,7 +3219,7 @@
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3243,7 +3243,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U33">
         <v>-1</v>
@@ -3255,7 +3255,7 @@
         <v>6</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y33">
         <v>6</v>
@@ -3284,10 +3284,10 @@
         <v>10</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J34">
         <v>-1</v>
@@ -3296,7 +3296,7 @@
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3320,7 +3320,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U34">
         <v>10</v>
@@ -3332,7 +3332,7 @@
         <v>9</v>
       </c>
       <c r="X34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y34">
         <v>10</v>
@@ -3361,10 +3361,10 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
         <v>-1</v>
@@ -3373,7 +3373,7 @@
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -3397,7 +3397,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U35">
         <v>10</v>
@@ -3432,13 +3432,13 @@
         <v>6</v>
       </c>
       <c r="F36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G36">
         <v>5</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I36">
         <v>-1</v>
@@ -3486,7 +3486,7 @@
         <v>6</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y36">
         <v>5</v>
@@ -3515,10 +3515,10 @@
         <v>8</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J37">
         <v>-1</v>
@@ -3527,7 +3527,7 @@
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M37">
         <v>-1</v>
@@ -3551,10 +3551,10 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V37">
         <v>8</v>
@@ -3643,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="I2">
         <v>11</v>
@@ -3698,22 +3698,22 @@
         <v>26</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F4">
         <v>76.47</v>
       </c>
       <c r="G4">
+        <v>23.53</v>
+      </c>
+      <c r="H4">
+        <v>6.9</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="H4">
-        <v>7.2</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
-      </c>
       <c r="J4">
-        <v>23.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3819,7 +3819,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3854,10 +3854,10 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -3874,10 +3874,10 @@
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -3888,36 +3888,36 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920008</v>
+        <v>22330051920010</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920010</v>
+        <v>22330051920011</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -3928,10 +3928,10 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920010</v>
+        <v>22330051920013</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
         <v>79</v>
@@ -3940,18 +3940,18 @@
         <v>90</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920011</v>
+        <v>22330051920015</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
         <v>80</v>
@@ -3968,33 +3968,33 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920007</v>
+        <v>22330051920017</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
         <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920013</v>
+        <v>22330051920019</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
         <v>93</v>
@@ -4008,13 +4008,13 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920015</v>
+        <v>22330051920322</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
         <v>94</v>
@@ -4028,202 +4028,42 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920015</v>
+        <v>22330051920026</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920017</v>
+        <v>22330051920028</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
       </c>
       <c r="F12" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920019</v>
-      </c>
-      <c r="B13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D13" t="s">
-        <v>96</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920019</v>
-      </c>
-      <c r="B14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D14" t="s">
-        <v>96</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>22330051920021</v>
-      </c>
-      <c r="B15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>22330051920322</v>
-      </c>
-      <c r="B16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" t="s">
-        <v>85</v>
-      </c>
-      <c r="D16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>22330051920322</v>
-      </c>
-      <c r="B17" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" t="s">
-        <v>98</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>22330051920026</v>
-      </c>
-      <c r="B18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18" t="s">
-        <v>99</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>22330051920028</v>
-      </c>
-      <c r="B19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" t="s">
-        <v>87</v>
-      </c>
-      <c r="D19" t="s">
-        <v>100</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>22330051920028</v>
-      </c>
-      <c r="B20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D20" t="s">
-        <v>100</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -4259,118 +4099,118 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>22330051920008</v>
+        <v>22330051920006</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>22330051920010</v>
+        <v>22330051920008</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>22330051920015</v>
+        <v>22330051920010</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>22330051920019</v>
+        <v>22330051920011</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>22330051920322</v>
+        <v>22330051920013</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>22330051920028</v>
+        <v>22330051920015</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>22330051920006</v>
+        <v>22330051920017</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -4378,16 +4218,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>22330051920011</v>
+        <v>22330051920019</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -4395,16 +4235,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>22330051920007</v>
+        <v>22330051920322</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -4412,16 +4252,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>22330051920013</v>
+        <v>22330051920026</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -4429,16 +4269,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920017</v>
+        <v>22330051920028</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -4446,50 +4286,50 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>22330051920021</v>
+        <v>22330051920002</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>22330051920026</v>
+        <v>22330051920003</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="D14" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>22330051920002</v>
+        <v>22330051920004</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C15" t="s">
         <v>116</v>
       </c>
       <c r="D15" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4497,16 +4337,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>22330051920003</v>
+        <v>22330051920001</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C16" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D16" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4514,16 +4354,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>22330051920004</v>
+        <v>22330051920005</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D17" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4531,13 +4371,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>22330051920001</v>
+        <v>22330051920009</v>
       </c>
       <c r="B18" t="s">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D18" t="s">
         <v>133</v>
@@ -4548,13 +4388,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>22330051920005</v>
+        <v>22330051920007</v>
       </c>
       <c r="B19" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C19" t="s">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="D19" t="s">
         <v>134</v>
@@ -4565,13 +4405,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>22330051920009</v>
+        <v>22330051920014</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D20" t="s">
         <v>135</v>
@@ -4582,13 +4422,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>22330051920014</v>
+        <v>22330051920016</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="C21" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D21" t="s">
         <v>136</v>
@@ -4599,13 +4439,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>22330051920016</v>
+        <v>22330051920320</v>
       </c>
       <c r="B22" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D22" t="s">
         <v>137</v>
@@ -4616,13 +4456,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22330051920320</v>
+        <v>22330051920018</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D23" t="s">
         <v>138</v>
@@ -4633,13 +4473,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>22330051920018</v>
+        <v>22330051920321</v>
       </c>
       <c r="B24" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="C24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D24" t="s">
         <v>139</v>
@@ -4650,13 +4490,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920321</v>
+        <v>22330051920012</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="C25" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="D25" t="s">
         <v>140</v>
@@ -4667,13 +4507,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920012</v>
+        <v>22330051920020</v>
       </c>
       <c r="B26" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C26" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D26" t="s">
         <v>141</v>
@@ -4684,13 +4524,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920020</v>
+        <v>22330051920021</v>
       </c>
       <c r="B27" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C27" t="s">
-        <v>126</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s">
         <v>142</v>
@@ -4704,10 +4544,10 @@
         <v>22330051920022</v>
       </c>
       <c r="B28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C28" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D28" t="s">
         <v>143</v>
@@ -4721,10 +4561,10 @@
         <v>22330051920023</v>
       </c>
       <c r="B29" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D29" t="s">
         <v>144</v>
@@ -4738,10 +4578,10 @@
         <v>22330051920024</v>
       </c>
       <c r="B30" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D30" t="s">
         <v>145</v>
@@ -4755,10 +4595,10 @@
         <v>22330051920025</v>
       </c>
       <c r="B31" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C31" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D31" t="s">
         <v>146</v>
@@ -4772,10 +4612,10 @@
         <v>22330051920326</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D32" t="s">
         <v>147</v>
@@ -4789,10 +4629,10 @@
         <v>22330051920330</v>
       </c>
       <c r="B33" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C33" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D33" t="s">
         <v>148</v>
@@ -4806,10 +4646,10 @@
         <v>22330051920027</v>
       </c>
       <c r="B34" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C34" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D34" t="s">
         <v>149</v>
@@ -4823,10 +4663,10 @@
         <v>22330051920332</v>
       </c>
       <c r="B35" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C35" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D35" t="s">
         <v>150</v>
@@ -4877,13 +4717,13 @@
         <v>22330051920007</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>134</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -4892,7 +4732,7 @@
         <v>57</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4900,13 +4740,13 @@
         <v>22330051920007</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>134</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4923,13 +4763,13 @@
         <v>22330051920013</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -4946,13 +4786,13 @@
         <v>22330051920013</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -4969,13 +4809,13 @@
         <v>22330051920026</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -4992,13 +4832,13 @@
         <v>22330051920026</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -5015,13 +4855,13 @@
         <v>22330051920003</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -5041,10 +4881,10 @@
         <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -5064,10 +4904,10 @@
         <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -5084,13 +4924,13 @@
         <v>22330051920320</v>
       </c>
       <c r="B11" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -5107,13 +4947,13 @@
         <v>22330051920017</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -5130,13 +4970,13 @@
         <v>22330051920321</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -5153,13 +4993,13 @@
         <v>22330051920021</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="C14" t="s">
         <v>67</v>
       </c>
       <c r="D14" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -5168,7 +5008,7 @@
         <v>57</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/1AM - Estadisticos 20221.xlsx
+++ b/grupos/1AM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="151">
   <si>
     <t>Materia</t>
   </si>
@@ -185,10 +185,10 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
     <t>Herrera Serrano Mayra Iliana</t>
@@ -980,10 +980,10 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>10</v>
@@ -1019,7 +1019,7 @@
         <v>10</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -1057,10 +1057,10 @@
         <v>7</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
         <v>6</v>
@@ -1093,7 +1093,7 @@
         <v>8</v>
       </c>
       <c r="V5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -1134,10 +1134,10 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>6</v>
@@ -1211,10 +1211,10 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -1250,7 +1250,7 @@
         <v>9</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -1288,10 +1288,10 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>7</v>
@@ -1324,10 +1324,10 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X8">
         <v>7</v>
@@ -1365,10 +1365,10 @@
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
         <v>6</v>
@@ -1401,10 +1401,10 @@
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>6</v>
@@ -1442,10 +1442,10 @@
         <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
         <v>6</v>
@@ -1478,10 +1478,10 @@
         <v>6</v>
       </c>
       <c r="V10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>5</v>
@@ -1519,10 +1519,10 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>6</v>
@@ -1596,10 +1596,10 @@
         <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>7</v>
@@ -1673,10 +1673,10 @@
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1709,7 +1709,7 @@
         <v>-1</v>
       </c>
       <c r="V13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W13">
         <v>7</v>
@@ -1750,10 +1750,10 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>7</v>
@@ -1786,10 +1786,10 @@
         <v>-1</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>7</v>
@@ -1827,10 +1827,10 @@
         <v>9</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
         <v>7</v>
@@ -1863,10 +1863,10 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -1904,10 +1904,10 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>6</v>
@@ -1943,7 +1943,7 @@
         <v>5</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>6</v>
@@ -1981,10 +1981,10 @@
         <v>9</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
         <v>7</v>
@@ -2017,7 +2017,7 @@
         <v>8</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -2058,10 +2058,10 @@
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
         <v>6</v>
@@ -2097,7 +2097,7 @@
         <v>5</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>5</v>
@@ -2135,10 +2135,10 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
         <v>9</v>
@@ -2171,7 +2171,7 @@
         <v>10</v>
       </c>
       <c r="V19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>9</v>
@@ -2212,10 +2212,10 @@
         <v>8</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2248,10 +2248,10 @@
         <v>9</v>
       </c>
       <c r="V20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>6</v>
@@ -2289,10 +2289,10 @@
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>6</v>
@@ -2325,10 +2325,10 @@
         <v>-1</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>6</v>
@@ -2366,10 +2366,10 @@
         <v>7</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>-1</v>
@@ -2402,10 +2402,10 @@
         <v>8</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -2443,10 +2443,10 @@
         <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
         <v>6</v>
@@ -2520,10 +2520,10 @@
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>6</v>
@@ -2597,10 +2597,10 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>10</v>
@@ -2633,10 +2633,10 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2674,10 +2674,10 @@
         <v>7</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
         <v>6</v>
@@ -2710,10 +2710,10 @@
         <v>8</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>5</v>
@@ -2751,10 +2751,10 @@
         <v>6</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>6</v>
@@ -2787,10 +2787,10 @@
         <v>8</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X27">
         <v>7</v>
@@ -2828,10 +2828,10 @@
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
         <v>6</v>
@@ -2867,7 +2867,7 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>5</v>
@@ -2905,10 +2905,10 @@
         <v>7</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
         <v>7</v>
@@ -2941,7 +2941,7 @@
         <v>9</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>8</v>
@@ -2982,10 +2982,10 @@
         <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
         <v>7</v>
@@ -3021,7 +3021,7 @@
         <v>8</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>8</v>
@@ -3059,10 +3059,10 @@
         <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
         <v>8</v>
@@ -3098,7 +3098,7 @@
         <v>9</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X31">
         <v>8</v>
@@ -3136,10 +3136,10 @@
         <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
         <v>9</v>
@@ -3175,7 +3175,7 @@
         <v>9</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>8</v>
@@ -3213,10 +3213,10 @@
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L33">
         <v>9</v>
@@ -3252,7 +3252,7 @@
         <v>5</v>
       </c>
       <c r="W33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X33">
         <v>8</v>
@@ -3290,10 +3290,10 @@
         <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
         <v>10</v>
@@ -3329,7 +3329,7 @@
         <v>9</v>
       </c>
       <c r="W34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X34">
         <v>10</v>
@@ -3367,10 +3367,10 @@
         <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
         <v>8</v>
@@ -3406,7 +3406,7 @@
         <v>8</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>8</v>
@@ -3444,10 +3444,10 @@
         <v>-1</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L36">
         <v>-1</v>
@@ -3521,10 +3521,10 @@
         <v>8</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L37">
         <v>6</v>
@@ -3557,7 +3557,7 @@
         <v>8</v>
       </c>
       <c r="V37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W37">
         <v>8</v>
@@ -3622,7 +3622,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
@@ -3634,27 +3634,27 @@
         <v>23</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F2">
         <v>67.65000000000001</v>
       </c>
       <c r="G2">
+        <v>32.35</v>
+      </c>
+      <c r="H2">
+        <v>6.8</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="H2">
-        <v>8.9</v>
-      </c>
-      <c r="I2">
-        <v>11</v>
-      </c>
       <c r="J2">
-        <v>32.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -3663,25 +3663,25 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>73.53</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="G3">
-        <v>26.47</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>32.35</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3759,19 +3759,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>88.23999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="G6">
-        <v>11.76</v>
+        <v>5.88</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3863,7 +3863,7 @@
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3883,7 +3883,7 @@
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3903,7 +3903,7 @@
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3923,7 +3923,7 @@
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3943,7 +3943,7 @@
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3963,7 +3963,7 @@
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3983,7 +3983,7 @@
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4003,7 +4003,7 @@
         <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4023,7 +4023,7 @@
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4043,7 +4043,7 @@
         <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4063,7 +4063,7 @@
         <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -4682,7 +4682,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4714,45 +4714,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920007</v>
+        <v>22330051920011</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920007</v>
+        <v>22330051920011</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4775,7 +4775,7 @@
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -4798,7 +4798,7 @@
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4821,7 +4821,7 @@
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -4844,7 +4844,7 @@
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4867,7 +4867,7 @@
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4890,7 +4890,7 @@
         <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -4898,22 +4898,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920011</v>
+        <v>22330051920017</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G10">
         <v>-1</v>
@@ -4921,22 +4921,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920320</v>
+        <v>22330051920321</v>
       </c>
       <c r="B11" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -4944,70 +4944,24 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920017</v>
+        <v>22330051920021</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920321</v>
-      </c>
-      <c r="B13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" t="s">
-        <v>123</v>
-      </c>
-      <c r="D13" t="s">
-        <v>139</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920021</v>
-      </c>
-      <c r="B14" t="s">
-        <v>107</v>
-      </c>
-      <c r="C14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" t="s">
-        <v>142</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>57</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AM - Estadisticos 20221.xlsx
+++ b/grupos/1AM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="151">
   <si>
     <t>Materia</t>
   </si>
@@ -989,7 +989,7 @@
         <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1066,7 +1066,7 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1143,7 +1143,7 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1220,7 +1220,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1256,7 +1256,7 @@
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1297,7 +1297,7 @@
         <v>7</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1374,7 +1374,7 @@
         <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1451,7 +1451,7 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1487,7 +1487,7 @@
         <v>5</v>
       </c>
       <c r="Y10">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1528,7 +1528,7 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1605,7 +1605,7 @@
         <v>7</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1641,7 +1641,7 @@
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1682,7 +1682,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1759,7 +1759,7 @@
         <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1836,7 +1836,7 @@
         <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1913,7 +1913,7 @@
         <v>6</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1990,7 +1990,7 @@
         <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2067,7 +2067,7 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2144,7 +2144,7 @@
         <v>9</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2180,7 +2180,7 @@
         <v>9</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2221,7 +2221,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2257,7 +2257,7 @@
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2298,7 +2298,7 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2375,7 +2375,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2452,7 +2452,7 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2529,7 +2529,7 @@
         <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2565,7 +2565,7 @@
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2606,7 +2606,7 @@
         <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2642,7 +2642,7 @@
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2683,7 +2683,7 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2719,7 +2719,7 @@
         <v>5</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2760,7 +2760,7 @@
         <v>6</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2837,7 +2837,7 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2873,7 +2873,7 @@
         <v>5</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2914,7 +2914,7 @@
         <v>7</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2950,7 +2950,7 @@
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2991,7 +2991,7 @@
         <v>7</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3027,7 +3027,7 @@
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3068,7 +3068,7 @@
         <v>8</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3145,7 +3145,7 @@
         <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3181,7 +3181,7 @@
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3222,7 +3222,7 @@
         <v>9</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3258,7 +3258,7 @@
         <v>8</v>
       </c>
       <c r="Y33">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3299,7 +3299,7 @@
         <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3376,7 +3376,7 @@
         <v>8</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3453,7 +3453,7 @@
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3489,7 +3489,7 @@
         <v>5</v>
       </c>
       <c r="Y36">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3530,7 +3530,7 @@
         <v>6</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3566,7 +3566,7 @@
         <v>6</v>
       </c>
       <c r="Y37">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3727,19 +3727,19 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>85.29000000000001</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="G5">
-        <v>14.71</v>
+        <v>11.76</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4682,7 +4682,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4760,45 +4760,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920013</v>
+        <v>22330051920007</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>134</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920013</v>
+        <v>22330051920007</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>134</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4806,16 +4806,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920026</v>
+        <v>22330051920013</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -4829,16 +4829,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920026</v>
+        <v>22330051920013</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -4852,22 +4852,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920003</v>
+        <v>22330051920021</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4875,39 +4875,39 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920006</v>
+        <v>22330051920021</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>142</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920017</v>
+        <v>22330051920322</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -4921,22 +4921,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920321</v>
+        <v>22330051920322</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>139</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -4944,24 +4944,139 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920021</v>
+        <v>22330051920026</v>
       </c>
       <c r="B12" t="s">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>142</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920026</v>
+      </c>
+      <c r="B13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" t="s">
+        <v>95</v>
+      </c>
+      <c r="E13" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920003</v>
+      </c>
+      <c r="B14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" t="s">
+        <v>115</v>
+      </c>
+      <c r="D14" t="s">
+        <v>130</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920006</v>
+      </c>
+      <c r="B15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" t="s">
+        <v>56</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920017</v>
+      </c>
+      <c r="B16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920321</v>
+      </c>
+      <c r="B17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D17" t="s">
+        <v>139</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AM - Estadisticos 20221.xlsx
+++ b/grupos/1AM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="151">
   <si>
     <t>Materia</t>
   </si>
@@ -1679,7 +1679,7 @@
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>6</v>
@@ -2218,7 +2218,7 @@
         <v>9</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>7</v>
@@ -2254,7 +2254,7 @@
         <v>8</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y20">
         <v>7</v>
@@ -2372,7 +2372,7 @@
         <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>7</v>
@@ -2408,7 +2408,7 @@
         <v>7</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>8</v>
@@ -3450,7 +3450,7 @@
         <v>6</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M36">
         <v>9</v>
@@ -3695,16 +3695,16 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>76.47</v>
+        <v>70.59</v>
       </c>
       <c r="G4">
-        <v>23.53</v>
+        <v>29.41</v>
       </c>
       <c r="H4">
         <v>6.9</v>
@@ -4682,7 +4682,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5036,47 +5036,93 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920017</v>
+        <v>22330051920320</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
+        <v>22330051920017</v>
+      </c>
+      <c r="B17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" t="s">
+        <v>92</v>
+      </c>
+      <c r="E17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" t="s">
+        <v>56</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920018</v>
+      </c>
+      <c r="B18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" t="s">
+        <v>122</v>
+      </c>
+      <c r="D18" t="s">
+        <v>138</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
         <v>22330051920321</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B19" t="s">
         <v>71</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C19" t="s">
         <v>123</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D19" t="s">
         <v>139</v>
       </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="E19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" t="s">
         <v>55</v>
       </c>
-      <c r="G17">
+      <c r="G19">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AM - Estadisticos 20221.xlsx
+++ b/grupos/1AM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="151">
   <si>
     <t>Materia</t>
   </si>
@@ -188,12 +188,12 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
-    <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
@@ -215,6 +215,21 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>ARGUELLES</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
@@ -224,33 +239,84 @@
     <t>CRUZ</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>GUERRA</t>
   </si>
   <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>MERINO</t>
+  </si>
+  <si>
     <t>PANZO</t>
   </si>
   <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>SARMIENTO</t>
   </si>
   <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>COYOHUA</t>
   </si>
   <si>
@@ -260,214 +326,148 @@
     <t>DIAZ</t>
   </si>
   <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
     <t>QUERO</t>
   </si>
   <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
     <t>JERONIMO</t>
   </si>
   <si>
+    <t>AVELINO</t>
+  </si>
+  <si>
+    <t>ROCETE</t>
+  </si>
+  <si>
     <t>SANTOS</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>MACARIO</t>
   </si>
   <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>GALVAN</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
     <t>GILES</t>
   </si>
   <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
     <t>MORA</t>
   </si>
   <si>
+    <t>RUBEN DE JESUS</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>CHRISTOPHER</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
     <t>EDER</t>
   </si>
   <si>
     <t>NORBERTO DAMIAN</t>
   </si>
   <si>
+    <t>LUIS FERNANDO</t>
+  </si>
+  <si>
     <t>DIEGO</t>
   </si>
   <si>
     <t>ANGELO</t>
   </si>
   <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
     <t>CRISTHIAN</t>
   </si>
   <si>
+    <t>ISABEL</t>
+  </si>
+  <si>
     <t>DIEGO JESUS</t>
   </si>
   <si>
+    <t>JESUS YAEL</t>
+  </si>
+  <si>
+    <t>GABAEL</t>
+  </si>
+  <si>
     <t>LUIS</t>
   </si>
   <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
     <t>DIERICK YAEL</t>
   </si>
   <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>JOSE FRANCISCO</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
     <t>SHERLIN</t>
   </si>
   <si>
+    <t>VALENTINA</t>
+  </si>
+  <si>
+    <t>DYLAN OSMAR</t>
+  </si>
+  <si>
+    <t>GABRIEL</t>
+  </si>
+  <si>
+    <t>GREGORIO</t>
+  </si>
+  <si>
     <t>SAUL AZAEL</t>
   </si>
   <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>ISAAC JOHAMET</t>
+  </si>
+  <si>
     <t>EIDAN JOSEPH</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>ARGUELLES</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>MERINO</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
-    <t>ROCETE</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>GALVAN</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>RUBEN DE JESUS</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>CHRISTOPHER</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>LUIS FERNANDO</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>ISABEL</t>
-  </si>
-  <si>
-    <t>JESUS YAEL</t>
-  </si>
-  <si>
-    <t>GABAEL</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>JOSE FRANCISCO</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>VALENTINA</t>
-  </si>
-  <si>
-    <t>DYLAN OSMAR</t>
-  </si>
-  <si>
-    <t>GABRIEL</t>
-  </si>
-  <si>
-    <t>GREGORIO</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>ISAAC JOHAMET</t>
   </si>
   <si>
     <t>CHRISTOPHER ANDRUS</t>
@@ -1344,7 +1344,7 @@
         <v>7</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1362,7 +1362,7 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1398,7 +1398,7 @@
         <v>8</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1498,7 +1498,7 @@
         <v>7</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D11">
         <v>5</v>
@@ -1516,7 +1516,7 @@
         <v>6</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
         <v>5</v>
@@ -1552,7 +1552,7 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>5</v>
@@ -1652,7 +1652,7 @@
         <v>9</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>6</v>
@@ -1670,7 +1670,7 @@
         <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>5</v>
@@ -1706,7 +1706,7 @@
         <v>8</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V13">
         <v>5</v>
@@ -1729,7 +1729,7 @@
         <v>7</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D14">
         <v>6</v>
@@ -1747,7 +1747,7 @@
         <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>5</v>
@@ -1783,7 +1783,7 @@
         <v>7</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>5</v>
@@ -1883,7 +1883,7 @@
         <v>7</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D16">
         <v>5</v>
@@ -1901,7 +1901,7 @@
         <v>6</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>5</v>
@@ -1937,7 +1937,7 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>5</v>
@@ -2037,7 +2037,7 @@
         <v>7</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D18">
         <v>5</v>
@@ -2055,7 +2055,7 @@
         <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
         <v>6</v>
@@ -2091,7 +2091,7 @@
         <v>7</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V18">
         <v>5</v>
@@ -2268,7 +2268,7 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <v>8</v>
@@ -2286,7 +2286,7 @@
         <v>7</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J21">
         <v>6</v>
@@ -2322,7 +2322,7 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>7</v>
@@ -2499,7 +2499,7 @@
         <v>7</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D24">
         <v>5</v>
@@ -2517,7 +2517,7 @@
         <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
         <v>5</v>
@@ -2553,7 +2553,7 @@
         <v>7</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V24">
         <v>5</v>
@@ -2807,7 +2807,7 @@
         <v>7</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -2825,7 +2825,7 @@
         <v>7</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J28">
         <v>6</v>
@@ -2861,7 +2861,7 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V28">
         <v>6</v>
@@ -3192,7 +3192,7 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -3210,7 +3210,7 @@
         <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J33">
         <v>6</v>
@@ -3246,7 +3246,7 @@
         <v>8</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V33">
         <v>5</v>
@@ -3423,7 +3423,7 @@
         <v>8</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -3441,7 +3441,7 @@
         <v>7</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J36">
         <v>5</v>
@@ -3477,7 +3477,7 @@
         <v>8</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V36">
         <v>5</v>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -3663,30 +3663,30 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>67.65000000000001</v>
+        <v>70.59</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>29.41</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>32.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -3695,19 +3695,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>70.59</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="G4">
-        <v>29.41</v>
+        <v>11.76</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3819,7 +3819,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3844,226 +3844,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920006</v>
-      </c>
-      <c r="B2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920008</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920010</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920011</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920013</v>
-      </c>
-      <c r="B6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920015</v>
-      </c>
-      <c r="B7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920017</v>
-      </c>
-      <c r="B8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920019</v>
-      </c>
-      <c r="B9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D9" t="s">
-        <v>93</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920322</v>
-      </c>
-      <c r="B10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D10" t="s">
-        <v>94</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920026</v>
-      </c>
-      <c r="B11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920028</v>
-      </c>
-      <c r="B12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" t="s">
-        <v>85</v>
-      </c>
-      <c r="D12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -4099,203 +3879,203 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>22330051920006</v>
+        <v>22330051920002</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>22330051920008</v>
+        <v>22330051920003</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>22330051920010</v>
+        <v>22330051920004</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>22330051920011</v>
+        <v>22330051920001</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>22330051920013</v>
+        <v>22330051920005</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>22330051920015</v>
+        <v>22330051920006</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>22330051920017</v>
+        <v>22330051920008</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>22330051920019</v>
+        <v>22330051920009</v>
       </c>
       <c r="B9" t="s">
         <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>22330051920322</v>
+        <v>22330051920010</v>
       </c>
       <c r="B10" t="s">
         <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>22330051920026</v>
+        <v>22330051920011</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920028</v>
+        <v>22330051920007</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>22330051920002</v>
+        <v>22330051920013</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4303,16 +4083,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>22330051920003</v>
+        <v>22330051920014</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -4320,16 +4100,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>22330051920004</v>
+        <v>22330051920015</v>
       </c>
       <c r="B15" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4337,13 +4117,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>22330051920001</v>
+        <v>22330051920016</v>
       </c>
       <c r="B16" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
         <v>131</v>
@@ -4354,13 +4134,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>22330051920005</v>
+        <v>22330051920320</v>
       </c>
       <c r="B17" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="D17" t="s">
         <v>132</v>
@@ -4371,13 +4151,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>22330051920009</v>
+        <v>22330051920017</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D18" t="s">
         <v>133</v>
@@ -4388,13 +4168,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>22330051920007</v>
+        <v>22330051920018</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="D19" t="s">
         <v>134</v>
@@ -4405,13 +4185,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>22330051920014</v>
+        <v>22330051920321</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D20" t="s">
         <v>135</v>
@@ -4422,13 +4202,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>22330051920016</v>
+        <v>22330051920019</v>
       </c>
       <c r="B21" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D21" t="s">
         <v>136</v>
@@ -4439,13 +4219,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>22330051920320</v>
+        <v>22330051920012</v>
       </c>
       <c r="B22" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="D22" t="s">
         <v>137</v>
@@ -4456,13 +4236,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22330051920018</v>
+        <v>22330051920020</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="D23" t="s">
         <v>138</v>
@@ -4473,13 +4253,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>22330051920321</v>
+        <v>22330051920021</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="D24" t="s">
         <v>139</v>
@@ -4490,13 +4270,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920012</v>
+        <v>22330051920022</v>
       </c>
       <c r="B25" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="D25" t="s">
         <v>140</v>
@@ -4507,13 +4287,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920020</v>
+        <v>22330051920322</v>
       </c>
       <c r="B26" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="D26" t="s">
         <v>141</v>
@@ -4524,13 +4304,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920021</v>
+        <v>22330051920023</v>
       </c>
       <c r="B27" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="D27" t="s">
         <v>142</v>
@@ -4541,13 +4321,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22330051920022</v>
+        <v>22330051920024</v>
       </c>
       <c r="B28" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="D28" t="s">
         <v>143</v>
@@ -4558,13 +4338,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>22330051920023</v>
+        <v>22330051920025</v>
       </c>
       <c r="B29" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="D29" t="s">
         <v>144</v>
@@ -4575,13 +4355,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>22330051920024</v>
+        <v>22330051920326</v>
       </c>
       <c r="B30" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D30" t="s">
         <v>145</v>
@@ -4592,13 +4372,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>22330051920025</v>
+        <v>22330051920026</v>
       </c>
       <c r="B31" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D31" t="s">
         <v>146</v>
@@ -4609,13 +4389,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>22330051920326</v>
+        <v>22330051920330</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s">
-        <v>127</v>
+        <v>89</v>
       </c>
       <c r="D32" t="s">
         <v>147</v>
@@ -4626,13 +4406,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>22330051920330</v>
+        <v>22330051920027</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="C33" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D33" t="s">
         <v>148</v>
@@ -4643,13 +4423,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>22330051920027</v>
+        <v>22330051920028</v>
       </c>
       <c r="B34" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="C34" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D34" t="s">
         <v>149</v>
@@ -4663,10 +4443,10 @@
         <v>22330051920332</v>
       </c>
       <c r="B35" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="C35" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="D35" t="s">
         <v>150</v>
@@ -4682,7 +4462,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4714,45 +4494,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920011</v>
+        <v>22330051920007</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920011</v>
+        <v>22330051920007</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4760,22 +4540,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920007</v>
+        <v>22330051920021</v>
       </c>
       <c r="B4" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4783,22 +4563,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920007</v>
+        <v>22330051920021</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4806,39 +4586,39 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920013</v>
+        <v>22330051920003</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920013</v>
+        <v>22330051920011</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -4852,22 +4632,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920021</v>
+        <v>22330051920013</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4875,22 +4655,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920021</v>
+        <v>22330051920320</v>
       </c>
       <c r="B9" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4898,45 +4678,45 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920322</v>
+        <v>22330051920018</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
         <v>56</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920322</v>
+        <v>22330051920321</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -4944,25 +4724,25 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920026</v>
+        <v>22330051920322</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>141</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
         <v>56</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -4970,13 +4750,13 @@
         <v>22330051920026</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -4985,144 +4765,6 @@
         <v>55</v>
       </c>
       <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920003</v>
-      </c>
-      <c r="B14" t="s">
-        <v>98</v>
-      </c>
-      <c r="C14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D14" t="s">
-        <v>130</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920006</v>
-      </c>
-      <c r="B15" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920320</v>
-      </c>
-      <c r="B16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" t="s">
-        <v>121</v>
-      </c>
-      <c r="D16" t="s">
-        <v>137</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>57</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920017</v>
-      </c>
-      <c r="B17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" t="s">
-        <v>81</v>
-      </c>
-      <c r="D17" t="s">
-        <v>92</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>56</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920018</v>
-      </c>
-      <c r="B18" t="s">
-        <v>104</v>
-      </c>
-      <c r="C18" t="s">
-        <v>122</v>
-      </c>
-      <c r="D18" t="s">
-        <v>138</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920321</v>
-      </c>
-      <c r="B19" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" t="s">
-        <v>123</v>
-      </c>
-      <c r="D19" t="s">
-        <v>139</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>55</v>
-      </c>
-      <c r="G19">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AM - Estadisticos 20221.xlsx
+++ b/grupos/1AM - Estadisticos 20221.xlsx
@@ -992,7 +992,7 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -1069,7 +1069,7 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -1146,7 +1146,7 @@
         <v>7</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1164,7 +1164,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U6">
         <v>9</v>
@@ -1223,7 +1223,7 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1300,7 +1300,7 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1377,7 +1377,7 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1454,7 +1454,7 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1472,7 +1472,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U10">
         <v>6</v>
@@ -1531,7 +1531,7 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1549,7 +1549,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U11">
         <v>6</v>
@@ -1608,7 +1608,7 @@
         <v>7</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1685,7 +1685,7 @@
         <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1703,7 +1703,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -1762,7 +1762,7 @@
         <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1780,7 +1780,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>7</v>
@@ -1839,7 +1839,7 @@
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1857,7 +1857,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>10</v>
@@ -1916,7 +1916,7 @@
         <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -1934,7 +1934,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>7</v>
@@ -1993,7 +1993,7 @@
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -2011,7 +2011,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>8</v>
@@ -2070,7 +2070,7 @@
         <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -2088,7 +2088,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -2147,7 +2147,7 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2224,7 +2224,7 @@
         <v>7</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2242,7 +2242,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U20">
         <v>9</v>
@@ -2301,7 +2301,7 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2378,7 +2378,7 @@
         <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2455,7 +2455,7 @@
         <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -2532,7 +2532,7 @@
         <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -2550,7 +2550,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U24">
         <v>5</v>
@@ -2609,7 +2609,7 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -2686,7 +2686,7 @@
         <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -2763,7 +2763,7 @@
         <v>6</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -2781,7 +2781,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U27">
         <v>8</v>
@@ -2840,7 +2840,7 @@
         <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -2917,7 +2917,7 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -2935,7 +2935,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U29">
         <v>9</v>
@@ -2994,7 +2994,7 @@
         <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -3071,7 +3071,7 @@
         <v>8</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O31">
         <v>-1</v>
@@ -3148,7 +3148,7 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
         <v>-1</v>
@@ -3225,7 +3225,7 @@
         <v>7</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O33">
         <v>-1</v>
@@ -3243,7 +3243,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U33">
         <v>7</v>
@@ -3302,7 +3302,7 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O34">
         <v>-1</v>
@@ -3320,7 +3320,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U34">
         <v>10</v>
@@ -3379,7 +3379,7 @@
         <v>9</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>-1</v>
@@ -3456,7 +3456,7 @@
         <v>9</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O36">
         <v>-1</v>
@@ -3474,7 +3474,7 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U36">
         <v>5</v>
@@ -3533,7 +3533,7 @@
         <v>9</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O37">
         <v>-1</v>
@@ -3551,7 +3551,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U37">
         <v>8</v>
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/1AM - Estadisticos 20221.xlsx
+++ b/grupos/1AM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="151">
   <si>
     <t>Materia</t>
   </si>
@@ -191,13 +191,13 @@
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
     <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
     <t>Zarate Amezcua Eladio Jorge</t>
@@ -995,7 +995,7 @@
         <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1007,7 +1007,7 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>9</v>
@@ -1072,7 +1072,7 @@
         <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1084,13 +1084,13 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
         <v>7</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>6</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1161,13 +1161,13 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
         <v>6</v>
       </c>
       <c r="U6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>5</v>
@@ -1226,7 +1226,7 @@
         <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1238,7 +1238,7 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>9</v>
@@ -1303,7 +1303,7 @@
         <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1315,7 +1315,7 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1333,7 +1333,7 @@
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1380,7 +1380,7 @@
         <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1392,13 +1392,13 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
         <v>8</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1457,7 +1457,7 @@
         <v>6</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1469,13 +1469,13 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T10">
         <v>6</v>
       </c>
       <c r="U10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>5</v>
@@ -1534,7 +1534,7 @@
         <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1546,7 +1546,7 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T11">
         <v>6</v>
@@ -1611,7 +1611,7 @@
         <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1623,13 +1623,13 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>9</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>6</v>
@@ -1688,7 +1688,7 @@
         <v>5</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1700,7 +1700,7 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
         <v>7</v>
@@ -1718,7 +1718,7 @@
         <v>5</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1765,7 +1765,7 @@
         <v>6</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1777,13 +1777,13 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T14">
         <v>6</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>5</v>
@@ -1842,7 +1842,7 @@
         <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1854,7 +1854,7 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
         <v>8</v>
@@ -1919,7 +1919,7 @@
         <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1931,7 +1931,7 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
         <v>6</v>
@@ -1996,7 +1996,7 @@
         <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2008,7 +2008,7 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>8</v>
@@ -2073,7 +2073,7 @@
         <v>6</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2085,13 +2085,13 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
         <v>6</v>
       </c>
       <c r="U18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>5</v>
@@ -2150,7 +2150,7 @@
         <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2162,7 +2162,7 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>8</v>
@@ -2180,7 +2180,7 @@
         <v>9</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2227,7 +2227,7 @@
         <v>6</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2239,13 +2239,13 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
         <v>6</v>
       </c>
       <c r="U20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -2304,7 +2304,7 @@
         <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2316,7 +2316,7 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>7</v>
@@ -2334,7 +2334,7 @@
         <v>6</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2381,7 +2381,7 @@
         <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2393,7 +2393,7 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
         <v>7</v>
@@ -2411,7 +2411,7 @@
         <v>5</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2458,7 +2458,7 @@
         <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2470,13 +2470,13 @@
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T23">
         <v>7</v>
       </c>
       <c r="U23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>5</v>
@@ -2535,7 +2535,7 @@
         <v>5</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2547,7 +2547,7 @@
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
         <v>6</v>
@@ -2612,7 +2612,7 @@
         <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2624,7 +2624,7 @@
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2689,7 +2689,7 @@
         <v>6</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2701,7 +2701,7 @@
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>7</v>
@@ -2719,7 +2719,7 @@
         <v>5</v>
       </c>
       <c r="Y26">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2766,7 +2766,7 @@
         <v>6</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2778,7 +2778,7 @@
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T27">
         <v>7</v>
@@ -2843,7 +2843,7 @@
         <v>6</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -2855,13 +2855,13 @@
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
         <v>7</v>
       </c>
       <c r="U28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>6</v>
@@ -2920,7 +2920,7 @@
         <v>7</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -2932,13 +2932,13 @@
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>9</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V29">
         <v>8</v>
@@ -2997,7 +2997,7 @@
         <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3009,7 +3009,7 @@
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -3074,7 +3074,7 @@
         <v>8</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3086,7 +3086,7 @@
         <v>-1</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
         <v>9</v>
@@ -3151,7 +3151,7 @@
         <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3163,7 +3163,7 @@
         <v>-1</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T32">
         <v>9</v>
@@ -3181,7 +3181,7 @@
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3228,7 +3228,7 @@
         <v>6</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3240,13 +3240,13 @@
         <v>-1</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T33">
         <v>7</v>
       </c>
       <c r="U33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V33">
         <v>5</v>
@@ -3258,7 +3258,7 @@
         <v>8</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3305,7 +3305,7 @@
         <v>8</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3317,7 +3317,7 @@
         <v>-1</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>9</v>
@@ -3382,7 +3382,7 @@
         <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3394,7 +3394,7 @@
         <v>-1</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -3459,7 +3459,7 @@
         <v>5</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3471,13 +3471,13 @@
         <v>-1</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T36">
         <v>7</v>
       </c>
       <c r="U36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V36">
         <v>5</v>
@@ -3536,7 +3536,7 @@
         <v>6</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -3548,7 +3548,7 @@
         <v>-1</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T37">
         <v>7</v>
@@ -3686,7 +3686,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -3695,16 +3695,16 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>88.23999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="G4">
-        <v>11.76</v>
+        <v>5.88</v>
       </c>
       <c r="H4">
         <v>8.1</v>
@@ -3718,7 +3718,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -3727,19 +3727,19 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>88.23999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="G5">
-        <v>11.76</v>
+        <v>5.88</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3750,7 +3750,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
@@ -3771,7 +3771,7 @@
         <v>5.88</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4462,7 +4462,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4540,22 +4540,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920021</v>
+        <v>22330051920015</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4563,22 +4563,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920021</v>
+        <v>22330051920015</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4586,16 +4586,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920003</v>
+        <v>22330051920028</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -4609,22 +4609,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920011</v>
+        <v>22330051920028</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4632,16 +4632,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920013</v>
+        <v>22330051920003</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920320</v>
+        <v>22330051920011</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4678,22 +4678,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920018</v>
+        <v>22330051920013</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920321</v>
+        <v>22330051920320</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -4724,16 +4724,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920322</v>
+        <v>22330051920018</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D12" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -4747,16 +4747,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920026</v>
+        <v>22330051920321</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -4765,6 +4765,75 @@
         <v>55</v>
       </c>
       <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920021</v>
+      </c>
+      <c r="B14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" t="s">
+        <v>139</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>56</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920322</v>
+      </c>
+      <c r="B15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" t="s">
+        <v>111</v>
+      </c>
+      <c r="D15" t="s">
+        <v>141</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>56</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920026</v>
+      </c>
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>115</v>
+      </c>
+      <c r="D16" t="s">
+        <v>146</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AM - Estadisticos 20221.xlsx
+++ b/grupos/1AM - Estadisticos 20221.xlsx
@@ -1004,7 +1004,7 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
         <v>10</v>
@@ -1081,7 +1081,7 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
         <v>9</v>
@@ -1235,7 +1235,7 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
         <v>8</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
         <v>8</v>
@@ -1389,7 +1389,7 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
         <v>7</v>
@@ -1620,7 +1620,7 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
         <v>8</v>
@@ -1869,7 +1869,7 @@
         <v>9</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -2005,7 +2005,7 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
         <v>8</v>
@@ -2159,7 +2159,7 @@
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
         <v>7</v>
@@ -2177,7 +2177,7 @@
         <v>9</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2621,7 +2621,7 @@
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
         <v>8</v>
@@ -3006,7 +3006,7 @@
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
         <v>10</v>
@@ -3083,7 +3083,7 @@
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
         <v>8</v>
@@ -3101,7 +3101,7 @@
         <v>10</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y31">
         <v>8</v>
@@ -3160,7 +3160,7 @@
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S32">
         <v>9</v>
@@ -3314,7 +3314,7 @@
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
         <v>10</v>
@@ -3391,7 +3391,7 @@
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S35">
         <v>10</v>
@@ -3545,7 +3545,7 @@
         <v>-1</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S37">
         <v>9</v>
@@ -3563,7 +3563,7 @@
         <v>8</v>
       </c>
       <c r="X37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y37">
         <v>9</v>

--- a/grupos/1AM - Estadisticos 20221.xlsx
+++ b/grupos/1AM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="151">
   <si>
     <t>Materia</t>
   </si>
@@ -188,16 +188,16 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
   </si>
   <si>
     <t>Zarate Amezcua Eladio Jorge</t>
@@ -998,7 +998,7 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -1075,7 +1075,7 @@
         <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -1152,13 +1152,13 @@
         <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
         <v>7</v>
@@ -1170,7 +1170,7 @@
         <v>8</v>
       </c>
       <c r="V6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>8</v>
@@ -1229,7 +1229,7 @@
         <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -1306,7 +1306,7 @@
         <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -1383,7 +1383,7 @@
         <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -1460,13 +1460,13 @@
         <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
         <v>6</v>
@@ -1484,7 +1484,7 @@
         <v>7</v>
       </c>
       <c r="X10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>6</v>
@@ -1537,13 +1537,13 @@
         <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S11">
         <v>5</v>
@@ -1614,7 +1614,7 @@
         <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1632,7 +1632,7 @@
         <v>7</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>8</v>
@@ -1691,13 +1691,13 @@
         <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
         <v>7</v>
@@ -1715,7 +1715,7 @@
         <v>7</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>6</v>
@@ -1768,13 +1768,13 @@
         <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
         <v>6</v>
@@ -1792,7 +1792,7 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>6</v>
@@ -1845,7 +1845,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -1922,13 +1922,13 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
         <v>7</v>
@@ -1940,7 +1940,7 @@
         <v>7</v>
       </c>
       <c r="V16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>7</v>
@@ -1999,7 +1999,7 @@
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -2017,7 +2017,7 @@
         <v>8</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -2076,13 +2076,13 @@
         <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
         <v>6</v>
@@ -2094,13 +2094,13 @@
         <v>6</v>
       </c>
       <c r="V18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>7</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -2153,7 +2153,7 @@
         <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -2230,13 +2230,13 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
         <v>7</v>
@@ -2254,7 +2254,7 @@
         <v>8</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>7</v>
@@ -2307,13 +2307,13 @@
         <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S21">
         <v>9</v>
@@ -2325,7 +2325,7 @@
         <v>8</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2384,13 +2384,13 @@
         <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
         <v>6</v>
@@ -2408,7 +2408,7 @@
         <v>7</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2461,13 +2461,13 @@
         <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
         <v>7</v>
@@ -2538,13 +2538,13 @@
         <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S24">
         <v>5</v>
@@ -2615,7 +2615,7 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -2692,13 +2692,13 @@
         <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
         <v>7</v>
@@ -2716,7 +2716,7 @@
         <v>9</v>
       </c>
       <c r="X26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>6</v>
@@ -2769,13 +2769,13 @@
         <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S27">
         <v>7</v>
@@ -2793,7 +2793,7 @@
         <v>10</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y27">
         <v>6</v>
@@ -2846,13 +2846,13 @@
         <v>9</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S28">
         <v>7</v>
@@ -2870,7 +2870,7 @@
         <v>7</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y28">
         <v>6</v>
@@ -2923,13 +2923,13 @@
         <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
         <v>10</v>
@@ -3000,7 +3000,7 @@
         <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -3077,7 +3077,7 @@
         <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -3154,7 +3154,7 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
         <v>-1</v>
@@ -3231,13 +3231,13 @@
         <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
         <v>6</v>
@@ -3249,13 +3249,13 @@
         <v>8</v>
       </c>
       <c r="V33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W33">
         <v>7</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y33">
         <v>6</v>
@@ -3308,7 +3308,7 @@
         <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q34">
         <v>-1</v>
@@ -3385,7 +3385,7 @@
         <v>9</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
         <v>-1</v>
@@ -3462,13 +3462,13 @@
         <v>8</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q36">
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S36">
         <v>6</v>
@@ -3486,7 +3486,7 @@
         <v>6</v>
       </c>
       <c r="X36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y36">
         <v>7</v>
@@ -3539,7 +3539,7 @@
         <v>9</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q37">
         <v>-1</v>
@@ -3557,7 +3557,7 @@
         <v>8</v>
       </c>
       <c r="V37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W37">
         <v>8</v>
@@ -3631,19 +3631,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>67.65000000000001</v>
+        <v>79.41</v>
       </c>
       <c r="G2">
-        <v>32.35</v>
+        <v>20.59</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -3663,19 +3663,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>70.59</v>
+        <v>94.12</v>
       </c>
       <c r="G3">
-        <v>29.41</v>
+        <v>5.88</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>8.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3686,7 +3686,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -3718,7 +3718,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -3739,7 +3739,7 @@
         <v>5.88</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3750,7 +3750,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
@@ -3771,7 +3771,7 @@
         <v>5.88</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4462,7 +4462,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4494,22 +4494,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920007</v>
+        <v>22330051920010</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4517,22 +4517,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920007</v>
+        <v>22330051920010</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4540,16 +4540,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920015</v>
+        <v>22330051920011</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -4563,22 +4563,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920015</v>
+        <v>22330051920007</v>
       </c>
       <c r="B5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" t="s">
         <v>75</v>
       </c>
-      <c r="C5" t="s">
-        <v>103</v>
-      </c>
       <c r="D5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4586,16 +4586,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920028</v>
+        <v>22330051920321</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -4621,219 +4621,12 @@
         <v>149</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920003</v>
-      </c>
-      <c r="B8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" t="s">
-        <v>93</v>
-      </c>
-      <c r="D8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920011</v>
-      </c>
-      <c r="B9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" t="s">
-        <v>100</v>
-      </c>
-      <c r="D9" t="s">
-        <v>126</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920013</v>
-      </c>
-      <c r="B10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" t="s">
-        <v>101</v>
-      </c>
-      <c r="D10" t="s">
-        <v>128</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920320</v>
-      </c>
-      <c r="B11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D11" t="s">
-        <v>132</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920018</v>
-      </c>
-      <c r="B12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" t="s">
-        <v>107</v>
-      </c>
-      <c r="D12" t="s">
-        <v>134</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920321</v>
-      </c>
-      <c r="B13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" t="s">
-        <v>108</v>
-      </c>
-      <c r="D13" t="s">
-        <v>135</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920021</v>
-      </c>
-      <c r="B14" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" t="s">
-        <v>139</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920322</v>
-      </c>
-      <c r="B15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C15" t="s">
-        <v>111</v>
-      </c>
-      <c r="D15" t="s">
-        <v>141</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920026</v>
-      </c>
-      <c r="B16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" t="s">
-        <v>115</v>
-      </c>
-      <c r="D16" t="s">
-        <v>146</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AM - Estadisticos 20221.xlsx
+++ b/grupos/1AM - Estadisticos 20221.xlsx
@@ -1001,7 +1001,7 @@
         <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>10</v>
@@ -1078,7 +1078,7 @@
         <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
         <v>8</v>
@@ -1155,7 +1155,7 @@
         <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
         <v>7</v>
@@ -1232,7 +1232,7 @@
         <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>10</v>
@@ -1309,7 +1309,7 @@
         <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>7</v>
@@ -1327,7 +1327,7 @@
         <v>7</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>7</v>
@@ -1386,7 +1386,7 @@
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
         <v>6</v>
@@ -1404,7 +1404,7 @@
         <v>7</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>6</v>
@@ -1463,7 +1463,7 @@
         <v>5</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
         <v>7</v>
@@ -1540,7 +1540,7 @@
         <v>5</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
         <v>5</v>
@@ -1617,7 +1617,7 @@
         <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
         <v>7</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
         <v>8</v>
@@ -1712,7 +1712,7 @@
         <v>5</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>6</v>
@@ -1771,7 +1771,7 @@
         <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
         <v>6</v>
@@ -1789,7 +1789,7 @@
         <v>5</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>6</v>
@@ -1848,7 +1848,7 @@
         <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
         <v>10</v>
@@ -1925,7 +1925,7 @@
         <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
         <v>6</v>
@@ -2002,7 +2002,7 @@
         <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>7</v>
@@ -2079,7 +2079,7 @@
         <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
         <v>7</v>
@@ -2097,7 +2097,7 @@
         <v>6</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>6</v>
@@ -2156,7 +2156,7 @@
         <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
         <v>7</v>
@@ -2233,7 +2233,7 @@
         <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
         <v>7</v>
@@ -2310,7 +2310,7 @@
         <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
         <v>6</v>
@@ -2387,7 +2387,7 @@
         <v>7</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>7</v>
@@ -2405,7 +2405,7 @@
         <v>7</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -2464,7 +2464,7 @@
         <v>6</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
         <v>6</v>
@@ -2541,7 +2541,7 @@
         <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
         <v>5</v>
@@ -2618,7 +2618,7 @@
         <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>10</v>
@@ -2695,7 +2695,7 @@
         <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>8</v>
@@ -2772,7 +2772,7 @@
         <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
         <v>6</v>
@@ -2790,7 +2790,7 @@
         <v>8</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X27">
         <v>6</v>
@@ -2849,7 +2849,7 @@
         <v>6</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>7</v>
@@ -2867,7 +2867,7 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>6</v>
@@ -2926,7 +2926,7 @@
         <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
         <v>9</v>
@@ -3003,7 +3003,7 @@
         <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
         <v>8</v>
@@ -3080,7 +3080,7 @@
         <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>10</v>
@@ -3157,7 +3157,7 @@
         <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R32">
         <v>8</v>
@@ -3175,7 +3175,7 @@
         <v>9</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X32">
         <v>8</v>
@@ -3234,7 +3234,7 @@
         <v>8</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>10</v>
@@ -3252,7 +3252,7 @@
         <v>6</v>
       </c>
       <c r="W33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>9</v>
@@ -3311,7 +3311,7 @@
         <v>9</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>10</v>
@@ -3388,7 +3388,7 @@
         <v>9</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R35">
         <v>8</v>
@@ -3465,7 +3465,7 @@
         <v>7</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R36">
         <v>8</v>
@@ -3542,7 +3542,7 @@
         <v>9</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
         <v>8</v>
